--- a/Data/Inventario/Stock Productos Comp. 10-6-2026.xlsx
+++ b/Data/Inventario/Stock Productos Comp. 10-6-2026.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="Rea68088fb02244a3"/>
+    <x:sheet name="Sheet1" sheetId="1" r:id="R3ff180f0ca3d46ac"/>
   </x:sheets>
 </x:workbook>
 </file>
